--- a/data/trans_bre/MCS12_SP_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 7,58</t>
+          <t>-0,3; 7,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 16,46</t>
+          <t>8,32; 16,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 9,65</t>
+          <t>0,6; 10,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,18</t>
+          <t>5,13; 15,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 15,09</t>
+          <t>-0,51; 15,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,54; 32,02</t>
+          <t>14,75; 32,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 17,84</t>
+          <t>1,16; 19,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 31,61</t>
+          <t>9,51; 32,13</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,48</t>
+          <t>10,51; 17,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 16,0</t>
+          <t>9,06; 15,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,86</t>
+          <t>3,52; 9,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 36,24</t>
+          <t>9,41; 34,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,94; 47,4</t>
+          <t>25,81; 47,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 34,94</t>
+          <t>18,41; 34,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 22,56</t>
+          <t>7,5; 22,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 129,54</t>
+          <t>24,0; 129,22</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 20,4</t>
+          <t>8,08; 20,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,92</t>
+          <t>2,55; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 12,17</t>
+          <t>-0,85; 11,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,49</t>
+          <t>1,39; 12,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 56,32</t>
+          <t>19,26; 56,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 38,78</t>
+          <t>5,06; 39,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 29,93</t>
+          <t>-1,88; 28,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 30,66</t>
+          <t>3,19; 33,1</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,38</t>
+          <t>8,51; 13,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,29</t>
+          <t>10,26; 15,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,26</t>
+          <t>4,27; 8,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 26,86</t>
+          <t>9,04; 26,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 32,03</t>
+          <t>19,18; 32,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 32,23</t>
+          <t>20,74; 32,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 19,74</t>
+          <t>8,64; 19,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 84,04</t>
+          <t>21,55; 79,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,08</t>
+          <t>12,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,57</t>
+          <t>-0,77; 7,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,75</t>
+          <t>8,33; 16,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 10,17</t>
+          <t>0,58; 9,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 15,3</t>
+          <t>6,96; 16,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,27</t>
+          <t>-1,26; 14,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 32,26</t>
+          <t>14,5; 32,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 19,21</t>
+          <t>0,97; 18,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 32,13</t>
+          <t>12,64; 35,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,94</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,56</t>
+          <t>10,44; 17,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 15,74</t>
+          <t>9,08; 15,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 9,72</t>
+          <t>3,36; 9,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 34,0</t>
+          <t>4,06; 10,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,81; 47,49</t>
+          <t>25,63; 47,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 34,62</t>
+          <t>18,77; 34,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,31</t>
+          <t>7,07; 21,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 129,22</t>
+          <t>9,67; 26,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>7,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 20,47</t>
+          <t>8,08; 21,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 16,41</t>
+          <t>2,57; 16,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 11,73</t>
+          <t>0,02; 12,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,54</t>
+          <t>2,51; 12,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,26; 56,07</t>
+          <t>18,87; 56,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 39,74</t>
+          <t>5,21; 38,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 28,57</t>
+          <t>-0,14; 29,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 33,1</t>
+          <t>5,71; 32,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,21</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,51</t>
+          <t>8,38; 13,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 15,31</t>
+          <t>10,6; 15,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,94</t>
+          <t>4,21; 9,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 26,27</t>
+          <t>6,5; 11,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,18; 32,16</t>
+          <t>18,68; 32,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 32,57</t>
+          <t>21,1; 32,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 19,09</t>
+          <t>8,57; 19,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,55; 79,85</t>
+          <t>15,0; 28,22</t>
         </is>
       </c>
     </row>
